--- a/results/GSE186332/selinexor_treatment_arm_sensitivity.xlsx
+++ b/results/GSE186332/selinexor_treatment_arm_sensitivity.xlsx
@@ -607,16 +607,16 @@
         <v>-0.02456567791523656</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06282286692662627</v>
+        <v>0.06282286692662624</v>
       </c>
       <c r="E2" t="n">
-        <v>0.211085530202351</v>
+        <v>0.2110855302023509</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.09053496729843569</v>
+        <v>-0.09053496729843558</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3035692459935511</v>
+        <v>0.3035692459935508</v>
       </c>
     </row>
     <row r="3">
@@ -632,16 +632,16 @@
         <v>-0.1405419733734229</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09695840886488695</v>
+        <v>-0.09695840886488694</v>
       </c>
       <c r="E3" t="n">
         <v>0.1867623895827806</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3855596391587646</v>
+        <v>-0.3855596391587647</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2386366811022367</v>
+        <v>0.2386366811022368</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1266908976462645</v>
+        <v>-0.1266908976462644</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1184024369015523</v>
@@ -666,7 +666,7 @@
         <v>-0.329928948359771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2518575374672229</v>
+        <v>0.2518575374672231</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.325687326512341</v>
+        <v>-0.3256873265123409</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1809984317866153</v>
+        <v>-0.1809984317866152</v>
       </c>
       <c r="E5" t="n">
         <v>0.2708745992075632</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5012702603247939</v>
+        <v>-0.5012702603247938</v>
       </c>
       <c r="G5" t="n">
         <v>0.3490853798274803</v>
@@ -753,13 +753,13 @@
         <v>2.884239258410827</v>
       </c>
       <c r="D2" t="n">
-        <v>0.236623017099221</v>
+        <v>0.2366230170992213</v>
       </c>
       <c r="E2" t="n">
-        <v>35.15649577010495</v>
+        <v>35.15649577010491</v>
       </c>
       <c r="F2" t="n">
-        <v>0.406389857413334</v>
+        <v>0.4063898574133339</v>
       </c>
     </row>
     <row r="3">
@@ -797,13 +797,13 @@
         <v>0.1270624534607467</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008493194418055981</v>
+        <v>0.008493194418055995</v>
       </c>
       <c r="E4" t="n">
-        <v>1.900918109815249</v>
+        <v>1.900918109815247</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1350145547121333</v>
+        <v>0.135014554712133</v>
       </c>
     </row>
     <row r="5">
@@ -816,16 +816,16 @@
         <v>-1.75678991031413</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1725980306484593</v>
+        <v>0.1725980306484592</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009757932769977572</v>
+        <v>0.009757932769977589</v>
       </c>
       <c r="E5" t="n">
-        <v>3.052908939420267</v>
+        <v>3.05290893942026</v>
       </c>
       <c r="F5" t="n">
-        <v>0.230709892917684</v>
+        <v>0.2307098929176835</v>
       </c>
     </row>
     <row r="6">
@@ -841,13 +841,13 @@
         <v>0.1859778316485511</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01210301495284611</v>
+        <v>0.01210301495284613</v>
       </c>
       <c r="E6" t="n">
-        <v>2.857779982876356</v>
+        <v>2.857779982876351</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2275481401036946</v>
+        <v>0.2275481401036943</v>
       </c>
     </row>
   </sheetData>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3035692459935511</v>
+        <v>0.3035692459935508</v>
       </c>
       <c r="C2" t="n">
-        <v>1.890327821111403</v>
+        <v>1.890327821111402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843569</v>
+        <v>-0.09053496729843558</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1536022691023406</v>
+        <v>0.1536022691023411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>-0.2540539747143987</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.5669879424213801</v>
+        <v>-0.5669879424213802</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.325687326512341</v>
+        <v>-0.3256873265123409</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.8826594532747007</v>
+        <v>-0.8826594532747005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>-0.02456567791523656</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4443135750350134</v>
+        <v>0.4443135750350135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3785271549791805</v>
+        <v>-0.3785271549791804</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.115512280438328</v>
+        <v>-1.115512280438327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.5012702603247939</v>
+        <v>-0.5012702603247938</v>
       </c>
       <c r="C13" t="n">
         <v>-1.656412580909693</v>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1669232286961848</v>
+        <v>-0.1669232286961846</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1830230217943296</v>
+        <v>-0.1830230217943289</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2148486011203608</v>
+        <v>-0.2148486011203609</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.3942189848705998</v>
+        <v>-0.3942189848706001</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.3855596391587646</v>
+        <v>-0.3855596391587647</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.14650280161739</v>
+        <v>-1.146502801617391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06489355131175112</v>
+        <v>-0.06489355131175117</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2665980220829754</v>
+        <v>0.2665980220829752</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>0.05396025482033245</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7903590860383858</v>
+        <v>0.7903590860383859</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1456968949337566</v>
+        <v>-0.1456968949337565</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.08948350869765191</v>
+        <v>-0.08948350869765143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3795170631755898</v>
+        <v>-0.3795170631755896</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.119874575488377</v>
+        <v>-1.119874575488376</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1197571205511969</v>
+        <v>0.1197571205511967</v>
       </c>
       <c r="C25" t="n">
-        <v>1.080310561061668</v>
+        <v>1.080310561061667</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3263959549847679</v>
+        <v>-0.3263959549847678</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.8857822140406026</v>
+        <v>-0.8857822140406025</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3409314871343583</v>
+        <v>-0.3409314871343582</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.9498369215134704</v>
+        <v>-0.9498369215134701</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1461892299385081</v>
+        <v>-0.146189229938508</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.09165311448734394</v>
+        <v>-0.0916531144873437</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1957735252430408</v>
+        <v>-0.1957735252430409</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3101595646326613</v>
+        <v>-0.3101595646326616</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>-0.2897718616821827</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.7243883580184677</v>
+        <v>-0.724388358018468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>-0.1405419733734229</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.06676696903508038</v>
+        <v>-0.06676696903508014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.09783912785934074</v>
+        <v>-0.09783912785934062</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1214145333353488</v>
+        <v>0.1214145333353493</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>-0.2871868164438909</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.7129966652452814</v>
+        <v>-0.7129966652452815</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>-0.2353514648807942</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4845703340344917</v>
+        <v>-0.4845703340344918</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>0.001004040388167093</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5569933730109207</v>
+        <v>0.5569933730109208</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.01875336389815385</v>
+        <v>-0.0187533638981538</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4699270902660449</v>
+        <v>0.4699270902660452</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.2386366811022367</v>
+        <v>0.2386366811022368</v>
       </c>
       <c r="C40" t="n">
         <v>1.604185118747848</v>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1768006485748422</v>
+        <v>0.1768006485748421</v>
       </c>
       <c r="C41" t="n">
         <v>1.33168811388679</v>
@@ -2436,7 +2436,7 @@
         <v>-0.1253328976907889</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0002558880407976535</v>
+        <v>0.0002558880407978982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>-0.172338913748451</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.2068886854809438</v>
+        <v>-0.2068886854809436</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2518575374672229</v>
+        <v>0.2518575374672231</v>
       </c>
       <c r="C44" t="n">
-        <v>1.662446355989434</v>
+        <v>1.662446355989435</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.1266908976462645</v>
+        <v>-0.1266908976462644</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.005728501729108614</v>
+        <v>-0.00572850172910837</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.02074949506060786</v>
+        <v>-0.02074949506060797</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4611306047729376</v>
+        <v>0.4611306047729372</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.2729567360682781</v>
+        <v>-0.272956736068278</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.6502880126555679</v>
+        <v>-0.6502880126555675</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>-0.2688431769778193</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.6321605150517656</v>
+        <v>-0.6321605150517657</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>-0.3481914504932407</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.9818298904967256</v>
+        <v>-0.9818298904967258</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>-0.329928948359771</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.9013512936456987</v>
+        <v>-0.9013512936456988</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/results/GSE186332/selinexor_treatment_arm_sensitivity.xlsx
+++ b/results/GSE186332/selinexor_treatment_arm_sensitivity.xlsx
@@ -604,19 +604,19 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02456567791523656</v>
+        <v>-0.02456567791523645</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06282286692662624</v>
+        <v>0.06282286692662632</v>
       </c>
       <c r="E2" t="n">
         <v>0.2110855302023509</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.09053496729843558</v>
+        <v>-0.09053496729843552</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3035692459935508</v>
+        <v>0.303569245993551</v>
       </c>
     </row>
     <row r="3">
@@ -629,19 +629,19 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1405419733734229</v>
+        <v>-0.1405419733734231</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09695840886488694</v>
+        <v>-0.09695840886488698</v>
       </c>
       <c r="E3" t="n">
         <v>0.1867623895827806</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3855596391587647</v>
+        <v>-0.3855596391587646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2386366811022368</v>
+        <v>0.2386366811022366</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1266908976462644</v>
+        <v>-0.1266908976462645</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1184024369015523</v>
@@ -666,7 +666,7 @@
         <v>-0.329928948359771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2518575374672231</v>
+        <v>0.2518575374672232</v>
       </c>
     </row>
     <row r="5">
@@ -679,10 +679,10 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3256873265123409</v>
+        <v>-0.325687326512341</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1809984317866152</v>
+        <v>-0.1809984317866153</v>
       </c>
       <c r="E5" t="n">
         <v>0.2708745992075632</v>
@@ -747,19 +747,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.059261176595679</v>
+        <v>1.05926117659568</v>
       </c>
       <c r="C2" t="n">
-        <v>2.884239258410827</v>
+        <v>2.88423925841083</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2366230170992213</v>
+        <v>0.2366230170992222</v>
       </c>
       <c r="E2" t="n">
-        <v>35.15649577010491</v>
+        <v>35.15649577010485</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4063898574133339</v>
+        <v>0.4063898574133328</v>
       </c>
     </row>
     <row r="3">
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2.063076553864201</v>
+        <v>-2.063076553864203</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1270624534607467</v>
+        <v>0.1270624534607465</v>
       </c>
       <c r="D4" t="n">
         <v>0.008493194418055995</v>
       </c>
       <c r="E4" t="n">
-        <v>1.900918109815247</v>
+        <v>1.900918109815241</v>
       </c>
       <c r="F4" t="n">
-        <v>0.135014554712133</v>
+        <v>0.1350145547121327</v>
       </c>
     </row>
     <row r="5">
@@ -813,19 +813,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.75678991031413</v>
+        <v>-1.756789910314131</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1725980306484592</v>
+        <v>0.172598030648459</v>
       </c>
       <c r="D5" t="n">
         <v>0.009757932769977589</v>
       </c>
       <c r="E5" t="n">
-        <v>3.05290893942026</v>
+        <v>3.052908939420251</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2307098929176835</v>
+        <v>0.2307098929176828</v>
       </c>
     </row>
     <row r="6">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.682127797057204</v>
+        <v>-1.682127797057205</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1859778316485511</v>
+        <v>0.1859778316485509</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01210301495284613</v>
+        <v>0.01210301495284614</v>
       </c>
       <c r="E6" t="n">
-        <v>2.857779982876351</v>
+        <v>2.857779982876341</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2275481401036943</v>
+        <v>0.2275481401036936</v>
       </c>
     </row>
   </sheetData>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3035692459935508</v>
+        <v>0.303569245993551</v>
       </c>
       <c r="C2" t="n">
-        <v>1.890327821111402</v>
+        <v>1.890327821111403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843558</v>
+        <v>-0.09053496729843552</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1536022691023411</v>
+        <v>0.1536022691023414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0006384040292134463</v>
+        <v>-0.0006384040292133353</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5497555026933404</v>
+        <v>0.5497555026933409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2540539747143987</v>
+        <v>-0.2540539747143988</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.5669879424213802</v>
+        <v>-0.566987942421381</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3256873265123409</v>
+        <v>-0.325687326512341</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.8826594532747005</v>
+        <v>-0.8826594532747009</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.190930439496977</v>
+        <v>0.1909304394969769</v>
       </c>
       <c r="C8" t="n">
         <v>1.393954814194397</v>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02456567791523656</v>
+        <v>-0.02456567791523645</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4443135750350135</v>
+        <v>0.444313575035014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3785271549791804</v>
+        <v>-0.3785271549791803</v>
       </c>
       <c r="C12" t="n">
         <v>-1.115512280438327</v>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1669232286961846</v>
+        <v>-0.1669232286961848</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1830230217943289</v>
+        <v>-0.1830230217943294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>-0.2148486011203609</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.3942189848706001</v>
+        <v>-0.3942189848706004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.3855596391587647</v>
+        <v>-0.3855596391587646</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.146502801617391</v>
+        <v>-1.14650280161739</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1456968949337565</v>
+        <v>-0.1456968949337566</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.08948350869765143</v>
+        <v>-0.08948350869765193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.285845185822498</v>
+        <v>0.2858451858224979</v>
       </c>
       <c r="C21" t="n">
         <v>1.812222012682484</v>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.191567206592782</v>
+        <v>0.1915672065927821</v>
       </c>
       <c r="C23" t="n">
         <v>1.396760898597113</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3795170631755896</v>
+        <v>-0.3795170631755898</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.119874575488376</v>
+        <v>-1.119874575488377</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1197571205511967</v>
+        <v>0.1197571205511969</v>
       </c>
       <c r="C25" t="n">
-        <v>1.080310561061667</v>
+        <v>1.080310561061668</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2897718616821827</v>
+        <v>-0.2897718616821826</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.724388358018468</v>
+        <v>-0.7243883580184676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1405419733734229</v>
+        <v>-0.1405419733734231</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.06676696903508014</v>
+        <v>-0.06676696903508088</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.09783912785934062</v>
+        <v>-0.09783912785934074</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1214145333353493</v>
+        <v>0.1214145333353489</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.001004040388167093</v>
+        <v>0.001004040388167204</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5569933730109208</v>
+        <v>0.5569933730109212</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.0187533638981538</v>
+        <v>-0.01875336389815396</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4699270902660452</v>
+        <v>0.4699270902660445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.2386366811022368</v>
+        <v>0.2386366811022366</v>
       </c>
       <c r="C40" t="n">
         <v>1.604185118747848</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1253328976907889</v>
+        <v>-0.125332897690789</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0002558880407978982</v>
+        <v>0.0002558880407971643</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>-0.172338913748451</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.2068886854809436</v>
+        <v>-0.2068886854809439</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2518575374672231</v>
+        <v>0.2518575374672232</v>
       </c>
       <c r="C44" t="n">
         <v>1.662446355989435</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.1266908976462644</v>
+        <v>-0.1266908976462645</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.00572850172910837</v>
+        <v>-0.005728501729108615</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.02074949506060797</v>
+        <v>-0.02074949506060786</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4611306047729372</v>
+        <v>0.4611306047729377</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.272956736068278</v>
+        <v>-0.2729567360682781</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.6502880126555675</v>
+        <v>-0.6502880126555679</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>-0.4639826633474022</v>
       </c>
       <c r="C51" t="n">
-        <v>-1.492094818603322</v>
+        <v>-1.492094818603323</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.3481914504932407</v>
+        <v>-0.3481914504932406</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.9818298904967258</v>
+        <v>-0.9818298904967252</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/results/GSE186332/selinexor_treatment_arm_sensitivity.xlsx
+++ b/results/GSE186332/selinexor_treatment_arm_sensitivity.xlsx
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6556316643188165</v>
+        <v>0.6556316643188164</v>
       </c>
     </row>
     <row r="9">
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3402193253539411</v>
+        <v>0.340219325353941</v>
       </c>
     </row>
     <row r="10">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2072078645416777</v>
+        <v>0.2072078645416776</v>
       </c>
     </row>
     <row r="12">
@@ -607,16 +607,16 @@
         <v>-0.02456567791523645</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06282286692662632</v>
+        <v>0.06282286692662629</v>
       </c>
       <c r="E2" t="n">
         <v>0.2110855302023509</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.09053496729843552</v>
+        <v>-0.09053496729843558</v>
       </c>
       <c r="G2" t="n">
-        <v>0.303569245993551</v>
+        <v>0.3035692459935509</v>
       </c>
     </row>
     <row r="3">
@@ -629,10 +629,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1405419733734231</v>
+        <v>-0.1405419733734229</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09695840886488698</v>
+        <v>-0.09695840886488696</v>
       </c>
       <c r="E3" t="n">
         <v>0.1867623895827806</v>
@@ -641,7 +641,7 @@
         <v>-0.3855596391587646</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2386366811022366</v>
+        <v>0.2386366811022367</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1266908976462645</v>
+        <v>-0.1266908976462644</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1184024369015523</v>
@@ -666,7 +666,7 @@
         <v>-0.329928948359771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2518575374672232</v>
+        <v>0.251857537467223</v>
       </c>
     </row>
     <row r="5">
@@ -682,16 +682,16 @@
         <v>-0.325687326512341</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1809984317866153</v>
+        <v>-0.1809984317866152</v>
       </c>
       <c r="E5" t="n">
         <v>0.2708745992075632</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5012702603247938</v>
+        <v>-0.5012702603247937</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3490853798274803</v>
+        <v>0.3490853798274802</v>
       </c>
     </row>
   </sheetData>
@@ -747,19 +747,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.05926117659568</v>
+        <v>1.059261176595681</v>
       </c>
       <c r="C2" t="n">
-        <v>2.88423925841083</v>
+        <v>2.884239258410834</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2366230170992222</v>
+        <v>0.2366230170992215</v>
       </c>
       <c r="E2" t="n">
-        <v>35.15649577010485</v>
+        <v>35.15649577010503</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4063898574133328</v>
+        <v>0.406389857413333</v>
       </c>
     </row>
     <row r="3">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.4221561350499611</v>
+        <v>-0.4221561350499614</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6556316643188165</v>
+        <v>0.6556316643188164</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3402193253539411</v>
+        <v>0.340219325353941</v>
       </c>
       <c r="E3" t="n">
         <v>1.263458149563584</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2072078645416777</v>
+        <v>0.2072078645416776</v>
       </c>
     </row>
     <row r="4">
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2.063076553864203</v>
+        <v>-2.063076553864204</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1270624534607465</v>
+        <v>0.1270624534607463</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008493194418055995</v>
+        <v>0.008493194418055966</v>
       </c>
       <c r="E4" t="n">
-        <v>1.900918109815241</v>
+        <v>1.900918109815244</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1350145547121327</v>
+        <v>0.1350145547121328</v>
       </c>
     </row>
     <row r="5">
@@ -813,19 +813,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.756789910314131</v>
+        <v>-1.756789910314132</v>
       </c>
       <c r="C5" t="n">
-        <v>0.172598030648459</v>
+        <v>0.1725980306484589</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009757932769977589</v>
+        <v>0.009757932769977554</v>
       </c>
       <c r="E5" t="n">
-        <v>3.052908939420251</v>
+        <v>3.052908939420257</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2307098929176828</v>
+        <v>0.2307098929176832</v>
       </c>
     </row>
     <row r="6">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.682127797057205</v>
+        <v>-1.682127797057206</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1859778316485509</v>
+        <v>0.1859778316485506</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01210301495284614</v>
+        <v>0.01210301495284607</v>
       </c>
       <c r="E6" t="n">
-        <v>2.857779982876341</v>
+        <v>2.857779982876349</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2275481401036936</v>
+        <v>0.2275481401036937</v>
       </c>
     </row>
   </sheetData>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.303569245993551</v>
+        <v>0.3035692459935509</v>
       </c>
       <c r="C2" t="n">
         <v>1.890327821111403</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843552</v>
+        <v>-0.09053496729843558</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1536022691023414</v>
+        <v>0.1536022691023411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0006384040292133353</v>
+        <v>-0.0006384040292134463</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5497555026933409</v>
+        <v>0.5497555026933404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3490853798274803</v>
+        <v>0.3490853798274802</v>
       </c>
       <c r="C5" t="n">
         <v>2.090906830398682</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2540539747143988</v>
+        <v>-0.2540539747143989</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.566987942421381</v>
+        <v>-0.5669879424213812</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>0.1058668675511346</v>
       </c>
       <c r="C10" t="n">
-        <v>1.019099448631347</v>
+        <v>1.019099448631348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3621064211877677</v>
+        <v>-0.3621064211877676</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.043149928054248</v>
+        <v>-1.043149928054247</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3785271549791803</v>
+        <v>-0.3785271549791804</v>
       </c>
       <c r="C12" t="n">
         <v>-1.115512280438327</v>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.5012702603247938</v>
+        <v>-0.5012702603247937</v>
       </c>
       <c r="C13" t="n">
         <v>-1.656412580909693</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.4000280024741703</v>
+        <v>-0.4000280024741704</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.210261511669543</v>
+        <v>-1.210261511669544</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1669232286961848</v>
+        <v>-0.1669232286961847</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1830230217943294</v>
+        <v>-0.1830230217943291</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06489355131175117</v>
+        <v>-0.06489355131175095</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2665980220829752</v>
+        <v>0.2665980220829762</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.05396025482033245</v>
+        <v>0.0539602548203324</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7903590860383859</v>
+        <v>0.7903590860383856</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2858451858224979</v>
+        <v>0.285845185822498</v>
       </c>
       <c r="C21" t="n">
         <v>1.812222012682484</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1989128906978094</v>
+        <v>-0.1989128906978095</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.3239940175984092</v>
+        <v>-0.3239940175984097</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1915672065927821</v>
+        <v>0.191567206592782</v>
       </c>
       <c r="C23" t="n">
         <v>1.396760898597113</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3795170631755898</v>
+        <v>-0.3795170631755896</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.119874575488377</v>
+        <v>-1.119874575488376</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3409314871343582</v>
+        <v>-0.3409314871343583</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.9498369215134701</v>
+        <v>-0.9498369215134705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.146189229938508</v>
+        <v>-0.1461892299385081</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0916531144873437</v>
+        <v>-0.09165311448734419</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2897718616821826</v>
+        <v>-0.2897718616821827</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.7243883580184676</v>
+        <v>-0.724388358018468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1405419733734231</v>
+        <v>-0.1405419733734229</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.06676696903508088</v>
+        <v>-0.06676696903508014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.09783912785934074</v>
+        <v>-0.09783912785934068</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1214145333353489</v>
+        <v>0.1214145333353491</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1537779986546591</v>
+        <v>0.153777998654659</v>
       </c>
       <c r="C35" t="n">
         <v>1.230232653521748</v>
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.2353514648807942</v>
+        <v>-0.2353514648807941</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4845703340344918</v>
+        <v>-0.4845703340344913</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.001004040388167204</v>
+        <v>0.001004040388167038</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5569933730109212</v>
+        <v>0.5569933730109206</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.01875336389815396</v>
+        <v>-0.01875336389815391</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4699270902660445</v>
+        <v>0.4699270902660447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.2386366811022366</v>
+        <v>0.2386366811022367</v>
       </c>
       <c r="C40" t="n">
         <v>1.604185118747848</v>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1768006485748421</v>
+        <v>0.176800648574842</v>
       </c>
       <c r="C41" t="n">
         <v>1.33168811388679</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.125332897690789</v>
+        <v>-0.1253328976907889</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0002558880407971643</v>
+        <v>0.0002558880407976535</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2518575374672232</v>
+        <v>0.251857537467223</v>
       </c>
       <c r="C44" t="n">
         <v>1.662446355989435</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.1266908976462645</v>
+        <v>-0.1266908976462644</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.005728501729108615</v>
+        <v>-0.00572850172910837</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.1656100261516483</v>
+        <v>-0.1656100261516482</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.1772360437891739</v>
+        <v>-0.1772360437891734</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.02074949506060786</v>
+        <v>-0.02074949506060797</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4611306047729377</v>
+        <v>0.4611306047729372</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.4531076962497638</v>
+        <v>-0.4531076962497637</v>
       </c>
       <c r="C49" t="n">
-        <v>-1.444171369427372</v>
+        <v>-1.444171369427371</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.3481914504932406</v>
+        <v>-0.3481914504932407</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.9818298904967252</v>
+        <v>-0.9818298904967258</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/results/GSE186332/selinexor_treatment_arm_sensitivity.xlsx
+++ b/results/GSE186332/selinexor_treatment_arm_sensitivity.xlsx
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.263458149563584</v>
+        <v>1.263458149563583</v>
       </c>
     </row>
     <row r="11">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2072078645416776</v>
+        <v>0.2072078645416775</v>
       </c>
     </row>
     <row r="12">
@@ -607,16 +607,16 @@
         <v>-0.02456567791523645</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06282286692662629</v>
+        <v>0.06282286692662627</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2110855302023509</v>
+        <v>0.211085530202351</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.09053496729843558</v>
+        <v>-0.09053496729843569</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3035692459935509</v>
+        <v>0.303569245993551</v>
       </c>
     </row>
     <row r="3">
@@ -629,10 +629,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1405419733734229</v>
+        <v>-0.1405419733734231</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09695840886488696</v>
+        <v>-0.09695840886488699</v>
       </c>
       <c r="E3" t="n">
         <v>0.1867623895827806</v>
@@ -666,7 +666,7 @@
         <v>-0.329928948359771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.251857537467223</v>
+        <v>0.2518575374672233</v>
       </c>
     </row>
     <row r="5">
@@ -688,10 +688,10 @@
         <v>0.2708745992075632</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5012702603247937</v>
+        <v>-0.5012702603247938</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3490853798274802</v>
+        <v>0.3490853798274803</v>
       </c>
     </row>
   </sheetData>
@@ -747,19 +747,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.059261176595681</v>
+        <v>1.05926117659568</v>
       </c>
       <c r="C2" t="n">
-        <v>2.884239258410834</v>
+        <v>2.884239258410831</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2366230170992215</v>
+        <v>0.2366230170992213</v>
       </c>
       <c r="E2" t="n">
-        <v>35.15649577010503</v>
+        <v>35.156495770105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.406389857413333</v>
+        <v>0.4063898574133334</v>
       </c>
     </row>
     <row r="3">
@@ -778,10 +778,10 @@
         <v>0.340219325353941</v>
       </c>
       <c r="E3" t="n">
-        <v>1.263458149563584</v>
+        <v>1.263458149563583</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2072078645416776</v>
+        <v>0.2072078645416775</v>
       </c>
     </row>
     <row r="4">
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2.063076553864204</v>
+        <v>-2.063076553864203</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1270624534607463</v>
+        <v>0.1270624534607465</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008493194418055966</v>
+        <v>0.008493194418055973</v>
       </c>
       <c r="E4" t="n">
-        <v>1.900918109815244</v>
+        <v>1.900918109815247</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1350145547121328</v>
+        <v>0.135014554712133</v>
       </c>
     </row>
     <row r="5">
@@ -813,19 +813,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.756789910314132</v>
+        <v>-1.756789910314131</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1725980306484589</v>
+        <v>0.172598030648459</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009757932769977554</v>
+        <v>0.009757932769977563</v>
       </c>
       <c r="E5" t="n">
-        <v>3.052908939420257</v>
+        <v>3.05290893942026</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2307098929176832</v>
+        <v>0.2307098929176834</v>
       </c>
     </row>
     <row r="6">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.682127797057206</v>
+        <v>-1.682127797057205</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1859778316485506</v>
+        <v>0.1859778316485509</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01210301495284607</v>
+        <v>0.01210301495284609</v>
       </c>
       <c r="E6" t="n">
-        <v>2.857779982876349</v>
+        <v>2.857779982876352</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2275481401036937</v>
+        <v>0.2275481401036942</v>
       </c>
     </row>
   </sheetData>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3035692459935509</v>
+        <v>0.303569245993551</v>
       </c>
       <c r="C2" t="n">
         <v>1.890327821111403</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843558</v>
+        <v>-0.09053496729843569</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1536022691023411</v>
+        <v>0.1536022691023406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3490853798274802</v>
+        <v>0.3490853798274803</v>
       </c>
       <c r="C5" t="n">
         <v>2.090906830398682</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2540539747143989</v>
+        <v>-0.2540539747143988</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.5669879424213812</v>
+        <v>-0.5669879424213806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1909304394969769</v>
+        <v>0.190930439496977</v>
       </c>
       <c r="C8" t="n">
         <v>1.393954814194397</v>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1058668675511346</v>
+        <v>0.1058668675511344</v>
       </c>
       <c r="C10" t="n">
-        <v>1.019099448631348</v>
+        <v>1.019099448631347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3785271549791804</v>
+        <v>-0.3785271549791803</v>
       </c>
       <c r="C12" t="n">
         <v>-1.115512280438327</v>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.5012702603247937</v>
+        <v>-0.5012702603247938</v>
       </c>
       <c r="C13" t="n">
         <v>-1.656412580909693</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.4000280024741704</v>
+        <v>-0.4000280024741703</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.210261511669544</v>
+        <v>-1.210261511669543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1669232286961847</v>
+        <v>-0.1669232286961848</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1830230217943291</v>
+        <v>-0.1830230217943296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>-0.2148486011203609</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.3942189848706004</v>
+        <v>-0.3942189848706001</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06489355131175095</v>
+        <v>-0.06489355131175106</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2665980220829762</v>
+        <v>0.2665980220829757</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0539602548203324</v>
+        <v>0.05396025482033245</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7903590860383856</v>
+        <v>0.7903590860383859</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1456968949337566</v>
+        <v>-0.1456968949337565</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.08948350869765193</v>
+        <v>-0.08948350869765143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1989128906978095</v>
+        <v>-0.1989128906978094</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.3239940175984097</v>
+        <v>-0.3239940175984092</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.191567206592782</v>
+        <v>0.1915672065927819</v>
       </c>
       <c r="C23" t="n">
-        <v>1.396760898597113</v>
+        <v>1.396760898597112</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3795170631755896</v>
+        <v>-0.3795170631755897</v>
       </c>
       <c r="C24" t="n">
         <v>-1.119874575488376</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1197571205511969</v>
+        <v>0.119757120551197</v>
       </c>
       <c r="C25" t="n">
         <v>1.080310561061668</v>
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3409314871343583</v>
+        <v>-0.3409314871343582</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.9498369215134705</v>
+        <v>-0.9498369215134701</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1461892299385081</v>
+        <v>-0.1461892299385082</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.09165311448734419</v>
+        <v>-0.09165311448734444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1957735252430409</v>
+        <v>-0.195773525243041</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3101595646326616</v>
+        <v>-0.3101595646326621</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1405419733734229</v>
+        <v>-0.1405419733734231</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.06676696903508014</v>
+        <v>-0.06676696903508111</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.09783912785934068</v>
+        <v>-0.09783912785934062</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1214145333353491</v>
+        <v>0.1214145333353493</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.2353514648807941</v>
+        <v>-0.2353514648807942</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4845703340344913</v>
+        <v>-0.4845703340344918</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.01875336389815391</v>
+        <v>-0.01875336389815396</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4699270902660447</v>
+        <v>0.4699270902660445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.176800648574842</v>
+        <v>0.1768006485748421</v>
       </c>
       <c r="C41" t="n">
         <v>1.33168811388679</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1253328976907889</v>
+        <v>-0.125332897690789</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0002558880407976535</v>
+        <v>0.0002558880407971643</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.251857537467223</v>
+        <v>0.2518575374672233</v>
       </c>
       <c r="C44" t="n">
-        <v>1.662446355989435</v>
+        <v>1.662446355989436</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.2729567360682781</v>
+        <v>-0.272956736068278</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.6502880126555679</v>
+        <v>-0.6502880126555675</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.4531076962497637</v>
+        <v>-0.4531076962497638</v>
       </c>
       <c r="C49" t="n">
-        <v>-1.444171369427371</v>
+        <v>-1.444171369427372</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>-0.4639826633474022</v>
       </c>
       <c r="C51" t="n">
-        <v>-1.492094818603323</v>
+        <v>-1.492094818603322</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/results/GSE186332/selinexor_treatment_arm_sensitivity.xlsx
+++ b/results/GSE186332/selinexor_treatment_arm_sensitivity.xlsx
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6556316643188164</v>
+        <v>0.6556316643188163</v>
       </c>
     </row>
     <row r="9">
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.340219325353941</v>
+        <v>0.3402193253539409</v>
       </c>
     </row>
     <row r="10">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2072078645416775</v>
+        <v>0.2072078645416774</v>
       </c>
     </row>
     <row r="12">
@@ -604,19 +604,19 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02456567791523645</v>
+        <v>-0.02456567791523639</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06282286692662627</v>
+        <v>0.06282286692662638</v>
       </c>
       <c r="E2" t="n">
-        <v>0.211085530202351</v>
+        <v>0.2110855302023509</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.09053496729843569</v>
+        <v>-0.09053496729843552</v>
       </c>
       <c r="G2" t="n">
-        <v>0.303569245993551</v>
+        <v>0.3035692459935511</v>
       </c>
     </row>
     <row r="3">
@@ -629,10 +629,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1405419733734231</v>
+        <v>-0.1405419733734229</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09695840886488699</v>
+        <v>-0.09695840886488698</v>
       </c>
       <c r="E3" t="n">
         <v>0.1867623895827806</v>
@@ -654,19 +654,19 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1266908976462644</v>
+        <v>-0.1266908976462642</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1184024369015523</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1784606746689361</v>
+        <v>0.178460674668936</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.329928948359771</v>
+        <v>-0.3299289483597709</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2518575374672233</v>
+        <v>0.251857537467223</v>
       </c>
     </row>
     <row r="5">
@@ -688,7 +688,7 @@
         <v>0.2708745992075632</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5012702603247938</v>
+        <v>-0.5012702603247936</v>
       </c>
       <c r="G5" t="n">
         <v>0.3490853798274803</v>
@@ -753,13 +753,13 @@
         <v>2.884239258410831</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2366230170992213</v>
+        <v>0.2366230170992223</v>
       </c>
       <c r="E2" t="n">
-        <v>35.156495770105</v>
+        <v>35.15649577010485</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4063898574133334</v>
+        <v>0.4063898574133327</v>
       </c>
     </row>
     <row r="3">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.4221561350499614</v>
+        <v>-0.4221561350499615</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6556316643188164</v>
+        <v>0.6556316643188163</v>
       </c>
       <c r="D3" t="n">
-        <v>0.340219325353941</v>
+        <v>0.3402193253539409</v>
       </c>
       <c r="E3" t="n">
         <v>1.263458149563583</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2072078645416775</v>
+        <v>0.2072078645416774</v>
       </c>
     </row>
     <row r="4">
@@ -794,16 +794,16 @@
         <v>-2.063076553864203</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1270624534607465</v>
+        <v>0.1270624534607464</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008493194418055973</v>
+        <v>0.008493194418055995</v>
       </c>
       <c r="E4" t="n">
-        <v>1.900918109815247</v>
+        <v>1.90091810981524</v>
       </c>
       <c r="F4" t="n">
-        <v>0.135014554712133</v>
+        <v>0.1350145547121325</v>
       </c>
     </row>
     <row r="5">
@@ -819,13 +819,13 @@
         <v>0.172598030648459</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009757932769977563</v>
+        <v>0.009757932769977598</v>
       </c>
       <c r="E5" t="n">
-        <v>3.05290893942026</v>
+        <v>3.05290893942025</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2307098929176834</v>
+        <v>0.2307098929176827</v>
       </c>
     </row>
     <row r="6">
@@ -841,13 +841,13 @@
         <v>0.1859778316485509</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01210301495284609</v>
+        <v>0.01210301495284614</v>
       </c>
       <c r="E6" t="n">
-        <v>2.857779982876352</v>
+        <v>2.85777998287634</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2275481401036942</v>
+        <v>0.2275481401036935</v>
       </c>
     </row>
   </sheetData>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.303569245993551</v>
+        <v>0.3035692459935511</v>
       </c>
       <c r="C2" t="n">
         <v>1.890327821111403</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843569</v>
+        <v>-0.09053496729843552</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1536022691023406</v>
+        <v>0.1536022691023413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0006384040292134463</v>
+        <v>-0.0006384040292133353</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5497555026933404</v>
+        <v>0.5497555026933408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>-0.2540539747143988</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.5669879424213806</v>
+        <v>-0.5669879424213808</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>-0.325687326512341</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.8826594532747009</v>
+        <v>-0.882659453274701</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.190930439496977</v>
+        <v>0.1909304394969768</v>
       </c>
       <c r="C8" t="n">
-        <v>1.393954814194397</v>
+        <v>1.393954814194396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02456567791523645</v>
+        <v>-0.02456567791523639</v>
       </c>
       <c r="C9" t="n">
-        <v>0.444313575035014</v>
+        <v>0.4443135750350141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1058668675511344</v>
+        <v>0.1058668675511345</v>
       </c>
       <c r="C10" t="n">
         <v>1.019099448631347</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3621064211877676</v>
+        <v>-0.3621064211877677</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.043149928054247</v>
+        <v>-1.043149928054248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.5012702603247938</v>
+        <v>-0.5012702603247936</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.656412580909693</v>
+        <v>-1.656412580909692</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.4000280024741703</v>
+        <v>-0.4000280024741701</v>
       </c>
       <c r="C14" t="n">
         <v>-1.210261511669543</v>
@@ -1410,7 +1410,7 @@
         <v>-0.1669232286961848</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1830230217943296</v>
+        <v>-0.1830230217943297</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2148486011203609</v>
+        <v>-0.214848601120361</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.3942189848706001</v>
+        <v>-0.3942189848706007</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06489355131175106</v>
+        <v>-0.06489355131175095</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2665980220829757</v>
+        <v>0.2665980220829761</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.05396025482033245</v>
+        <v>0.05396025482033234</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7903590860383859</v>
+        <v>0.7903590860383852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1456968949337565</v>
+        <v>-0.1456968949337566</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.08948350869765143</v>
+        <v>-0.08948350869765204</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.285845185822498</v>
+        <v>0.2858451858224981</v>
       </c>
       <c r="C21" t="n">
         <v>1.812222012682484</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1989128906978094</v>
+        <v>-0.1989128906978095</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.3239940175984092</v>
+        <v>-0.3239940175984101</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1915672065927819</v>
+        <v>0.191567206592782</v>
       </c>
       <c r="C23" t="n">
-        <v>1.396760898597112</v>
+        <v>1.396760898597113</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3795170631755897</v>
+        <v>-0.3795170631755898</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.119874575488376</v>
+        <v>-1.119874575488377</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>-0.3263959549847678</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.8857822140406025</v>
+        <v>-0.8857822140406024</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>-0.3409314871343582</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.9498369215134701</v>
+        <v>-0.9498369215134702</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1461892299385082</v>
+        <v>-0.1461892299385081</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.09165311448734444</v>
+        <v>-0.09165311448734406</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>-0.195773525243041</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3101595646326621</v>
+        <v>-0.3101595646326622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2897718616821827</v>
+        <v>-0.2897718616821825</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.724388358018468</v>
+        <v>-0.7243883580184671</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1405419733734231</v>
+        <v>-0.1405419733734229</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.06676696903508111</v>
+        <v>-0.0667669690350805</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>-0.09783912785934062</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1214145333353493</v>
+        <v>0.1214145333353492</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>0.153777998654659</v>
       </c>
       <c r="C35" t="n">
-        <v>1.230232653521748</v>
+        <v>1.230232653521747</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>-0.2871868164438909</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.7129966652452815</v>
+        <v>-0.7129966652452816</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>-0.2353514648807942</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4845703340344918</v>
+        <v>-0.484570334034492</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>0.001004040388167038</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5569933730109206</v>
+        <v>0.5569933730109203</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>-0.01875336389815396</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4699270902660445</v>
+        <v>0.4699270902660443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1768006485748421</v>
+        <v>0.176800648574842</v>
       </c>
       <c r="C41" t="n">
         <v>1.33168811388679</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.125332897690789</v>
+        <v>-0.1253328976907889</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0002558880407971643</v>
+        <v>0.0002558880407975312</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.172338913748451</v>
+        <v>-0.1723389137484508</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.2068886854809439</v>
+        <v>-0.2068886854809432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2518575374672233</v>
+        <v>0.251857537467223</v>
       </c>
       <c r="C44" t="n">
-        <v>1.662446355989436</v>
+        <v>1.662446355989434</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.1266908976462644</v>
+        <v>-0.1266908976462642</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.00572850172910837</v>
+        <v>-0.005728501729107759</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.1656100261516482</v>
+        <v>-0.1656100261516483</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.1772360437891734</v>
+        <v>-0.177236043789174</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.02074949506060797</v>
+        <v>-0.02074949506060808</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4611306047729372</v>
+        <v>0.4611306047729365</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>-0.272956736068278</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.6502880126555675</v>
+        <v>-0.6502880126555676</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.4531076962497638</v>
+        <v>-0.4531076962497637</v>
       </c>
       <c r="C49" t="n">
         <v>-1.444171369427372</v>
@@ -2740,7 +2740,7 @@
         <v>-0.2688431769778193</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.6321605150517657</v>
+        <v>-0.6321605150517658</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.4639826633474022</v>
+        <v>-0.4639826633474023</v>
       </c>
       <c r="C51" t="n">
-        <v>-1.492094818603322</v>
+        <v>-1.492094818603323</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>-0.3481914504932407</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.9818298904967258</v>
+        <v>-0.9818298904967259</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.329928948359771</v>
+        <v>-0.3299289483597709</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.9013512936456988</v>
+        <v>-0.9013512936456984</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
